--- a/backend/src/templates/template-giang-vien.xlsx
+++ b/backend/src/templates/template-giang-vien.xlsx
@@ -4,104 +4,80 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Danh sách giảng viên" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="DS CBGV Khoa CNTT" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>Mã giảng viên</t>
-  </si>
-  <si>
-    <t>Họ tên</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>MÃ ĐỊNH DANH MỚI</t>
+  </si>
+  <si>
+    <t>HỌ VÀ TÊN</t>
+  </si>
+  <si>
+    <t>NGÀY SINH</t>
+  </si>
+  <si>
+    <t>PHÒNG BAN</t>
+  </si>
+  <si>
+    <t>HỌC VỊ</t>
+  </si>
+  <si>
+    <t>Chức danh</t>
+  </si>
+  <si>
+    <t>Chức vụ</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Căn cước công dân</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Mật khẩu</t>
-  </si>
-  <si>
-    <t>Khoa</t>
-  </si>
-  <si>
-    <t>Bộ môn</t>
-  </si>
-  <si>
-    <t>Chức vụ</t>
-  </si>
-  <si>
-    <t>Học vị</t>
-  </si>
-  <si>
-    <t>Chuyên môn</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Email cá nhân</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>Kinh nghiệm làm việc</t>
-  </si>
-  <si>
-    <t>Bằng cấp</t>
-  </si>
-  <si>
-    <t>GV001</t>
-  </si>
-  <si>
-    <t>TS. Trần Thị B</t>
-  </si>
-  <si>
-    <t>gv001@dainam.edu.vn</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Công nghệ thông tin</t>
-  </si>
-  <si>
-    <t>Khoa học máy tính</t>
-  </si>
-  <si>
-    <t>Giảng viên</t>
-  </si>
-  <si>
-    <t>Tiến sĩ</t>
-  </si>
-  <si>
-    <t>Trí tuệ nhân tạo, Machine Learning</t>
-  </si>
-  <si>
-    <t>0987654321</t>
-  </si>
-  <si>
-    <t>tranthib@gmail.com</t>
-  </si>
-  <si>
-    <t>Hà Nội</t>
-  </si>
-  <si>
-    <t>5 năm giảng dạy</t>
-  </si>
-  <si>
-    <t>Tiến sĩ CNTT</t>
+    <t>Chuyên môn đào tạo</t>
+  </si>
+  <si>
+    <t>99900009</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>12/29/1991</t>
+  </si>
+  <si>
+    <t>Khoa Công nghệ thông tin</t>
+  </si>
+  <si>
+    <t>Thạc sĩ</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>966751676</t>
+  </si>
+  <si>
+    <t>CNTT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -111,6 +87,13 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="3">
@@ -122,11 +105,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6FFE6"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -134,13 +117,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,10 +473,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,58 +527,47 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
